--- a/employees_TX.xlsx
+++ b/employees_TX.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
   <si>
     <t>Legal Name</t>
   </si>
@@ -58,18 +58,12 @@
     <t>Lin</t>
   </si>
   <si>
-    <t>Zhiyu</t>
-  </si>
-  <si>
     <t>Fan</t>
   </si>
   <si>
     <t>Ma</t>
   </si>
   <si>
-    <t>Zhou</t>
-  </si>
-  <si>
     <t>Active</t>
   </si>
   <si>
@@ -79,7 +73,7 @@
     <t>Hourly</t>
   </si>
   <si>
-    <t>Receiving - Receiving</t>
+    <t>Inbound - Department Inbound</t>
   </si>
 </sst>
 </file>
@@ -415,7 +409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -464,22 +458,22 @@
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G2" s="1">
         <v>45692</v>
       </c>
       <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
         <v>19</v>
-      </c>
-      <c r="I2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -496,54 +490,22 @@
         <v>13</v>
       </c>
       <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
         <v>16</v>
-      </c>
-      <c r="F3" t="s">
-        <v>18</v>
       </c>
       <c r="G3" s="1">
         <v>46233</v>
       </c>
       <c r="H3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" t="s">
         <v>19</v>
-      </c>
-      <c r="I3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="1">
-        <v>45698</v>
-      </c>
-      <c r="H4" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
